--- a/artfynd/A 60375-2021 artfynd.xlsx
+++ b/artfynd/A 60375-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60375-2021 artfynd.xlsx
+++ b/artfynd/A 60375-2021 artfynd.xlsx
@@ -6466,7 +6466,7 @@
         <v>87185868</v>
       </c>
       <c r="B53" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>

--- a/artfynd/A 60375-2021 artfynd.xlsx
+++ b/artfynd/A 60375-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86513346</v>
+        <v>88459050</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519951.9481046536</v>
+        <v>520130</v>
       </c>
       <c r="R2" t="n">
-        <v>7201615.079672734</v>
+        <v>7201941</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Anders Hällström</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86513305</v>
+        <v>87185845</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Vijnievaartoe NO, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520346.1122553949</v>
+        <v>520463</v>
       </c>
       <c r="R3" t="n">
-        <v>7201845.891082902</v>
+        <v>7201294</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,58 +853,48 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Anders Hällström</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Linnea Helmersson, Caspar Ström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86513344</v>
+        <v>88459049</v>
       </c>
       <c r="B4" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519913.0308362714</v>
+        <v>520130</v>
       </c>
       <c r="R4" t="n">
-        <v>7201656.805324724</v>
+        <v>7201941</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,36 +950,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Anders Hällström</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86513345</v>
+        <v>88459168</v>
       </c>
       <c r="B5" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519951.0451537556</v>
+        <v>520334</v>
       </c>
       <c r="R5" t="n">
-        <v>7201623.131445269</v>
+        <v>7202301</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,36 +1047,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Anders Hällström</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86513343</v>
+        <v>88470670</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Vijnievaartoe NO, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519922.1766696509</v>
+        <v>520005</v>
       </c>
       <c r="R6" t="n">
-        <v>7201686.128275497</v>
+        <v>7201317</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,74 +1144,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Anders Hällström</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Linnea Helmersson, Caspar Ström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>87185850</v>
+        <v>88459171</v>
       </c>
       <c r="B7" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1506</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520461.9768903113</v>
+        <v>520320</v>
       </c>
       <c r="R7" t="n">
-        <v>7201294.076206806</v>
+        <v>7202316</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,65 +1245,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Caspar Ström, Linnea Helmersson</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>87185949</v>
+        <v>88404268</v>
       </c>
       <c r="B8" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bije-lite, V, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519891.0401644811</v>
+        <v>520349</v>
       </c>
       <c r="R8" t="n">
-        <v>7201388.198422908</v>
+        <v>7202342</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,27 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Caspar Ström, Linnea Helmersson</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>87185933</v>
+        <v>88459034</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520060.0628493036</v>
+        <v>520917</v>
       </c>
       <c r="R9" t="n">
-        <v>7201449.129066895</v>
+        <v>7201311</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,65 +1439,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Caspar Ström, Linnea Helmersson</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>87185848</v>
+        <v>88459037</v>
       </c>
       <c r="B10" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519906.0300437903</v>
+        <v>520912</v>
       </c>
       <c r="R10" t="n">
-        <v>7201432.83121557</v>
+        <v>7201347</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,27 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Caspar Ström, Linnea Helmersson</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>87185845</v>
+        <v>88459167</v>
       </c>
       <c r="B11" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520462.8261600752</v>
+        <v>520334</v>
       </c>
       <c r="R11" t="n">
-        <v>7201294.082019023</v>
+        <v>7202301</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,22 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,65 +1633,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Caspar Ström, Linnea Helmersson</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>87185837</v>
+        <v>86513305</v>
       </c>
       <c r="B12" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519915.160782393</v>
+        <v>520346</v>
       </c>
       <c r="R12" t="n">
-        <v>7201337.039157904</v>
+        <v>7201846</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1890,22 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,69 +1726,69 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Caspar Ström, Linnea Helmersson</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>87185935</v>
+        <v>86513343</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519990.8807939808</v>
+        <v>519922</v>
       </c>
       <c r="R13" t="n">
-        <v>7201317.185948584</v>
+        <v>7201686</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2002,22 +1812,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,35 +1828,35 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Caspar Ström, Linnea Helmersson</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>87185919</v>
+        <v>86513345</v>
       </c>
       <c r="B14" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2080,17 +1880,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519958.9681936665</v>
+        <v>519951</v>
       </c>
       <c r="R14" t="n">
-        <v>7201453.966006977</v>
+        <v>7201623</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2114,22 +1914,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,53 +1930,53 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Caspar Ström, Linnea Helmersson</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>87185841</v>
+        <v>87185919</v>
       </c>
       <c r="B15" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520035.2073038326</v>
+        <v>519959</v>
       </c>
       <c r="R15" t="n">
-        <v>7201292.882573353</v>
+        <v>7201454</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2229,19 +2019,9 @@
           <t>2020-07-28</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,53 +2048,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>88404496</v>
+        <v>88459043</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bije-lite, V, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520385.3953049071</v>
+        <v>520716</v>
       </c>
       <c r="R16" t="n">
-        <v>7202311.320225596</v>
+        <v>7201521</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2341,19 +2116,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,7 +2133,7 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -2380,58 +2145,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>88404310</v>
+        <v>88459045</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bije-lite, V, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520150.6075671606</v>
+        <v>520745</v>
       </c>
       <c r="R17" t="n">
-        <v>7201875.523242021</v>
+        <v>7201476</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,19 +2213,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,7 +2230,7 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2497,53 +2242,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>88404247</v>
+        <v>88459048</v>
       </c>
       <c r="B18" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bije-lite, V, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520155.273315287</v>
+        <v>520130</v>
       </c>
       <c r="R18" t="n">
-        <v>7201939.162843896</v>
+        <v>7201941</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2570,19 +2310,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,7 +2327,7 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2609,53 +2339,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>88404364</v>
+        <v>88459052</v>
       </c>
       <c r="B19" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4660</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bije-lite, V, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520899.5476899893</v>
+        <v>520156</v>
       </c>
       <c r="R19" t="n">
-        <v>7201390.412650047</v>
+        <v>7201849</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2682,19 +2407,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,7 +2424,7 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -2721,58 +2436,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>88404318</v>
+        <v>88470666</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bije-lite, V, Ås lm</t>
+          <t>Vijnievaartoe NO, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520210.9464207326</v>
+        <v>520041</v>
       </c>
       <c r="R20" t="n">
-        <v>7202119.330508539</v>
+        <v>7201294</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2796,22 +2501,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2826,27 +2521,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Linnea Helmersson, Caspar Ström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>88404552</v>
+        <v>86513344</v>
       </c>
       <c r="B21" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,37 +2544,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bije-lite, V, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520431.1751707626</v>
+        <v>519913</v>
       </c>
       <c r="R21" t="n">
-        <v>7202259.056659487</v>
+        <v>7201657</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2908,22 +2598,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2934,31 +2614,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>88459169</v>
+        <v>88404552</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,37 +2646,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Bije-lite, V, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520391.8465519027</v>
+        <v>520431</v>
       </c>
       <c r="R22" t="n">
-        <v>7202299.068278749</v>
+        <v>7202259</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3023,19 +2703,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3050,7 +2720,7 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3062,15 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>88459052</v>
+        <v>87185841</v>
       </c>
       <c r="B23" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,37 +2743,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Vijnievaartoe NO, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520155.8823251429</v>
+        <v>520035</v>
       </c>
       <c r="R23" t="n">
-        <v>7201848.842980376</v>
+        <v>7201293</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3132,22 +2797,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,27 +2817,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Linnea Helmersson, Caspar Ström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>88459044</v>
+        <v>88459042</v>
       </c>
       <c r="B24" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3190,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3214,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520745.1373198324</v>
+        <v>520725</v>
       </c>
       <c r="R24" t="n">
-        <v>7201489.854126956</v>
+        <v>7201492</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3247,19 +2897,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3286,53 +2926,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>88459048</v>
+        <v>87185850</v>
       </c>
       <c r="B25" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>1506</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Vijnievaartoe NO, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520130.2109879408</v>
+        <v>520462</v>
       </c>
       <c r="R25" t="n">
-        <v>7201941.114205981</v>
+        <v>7201294</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3356,22 +2991,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3386,27 +3011,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Linnea Helmersson, Caspar Ström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>88470658</v>
+        <v>88470669</v>
       </c>
       <c r="B26" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3414,21 +3034,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3438,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519891.9415604182</v>
+        <v>519956</v>
       </c>
       <c r="R26" t="n">
-        <v>7201444.188689304</v>
+        <v>7201348</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3471,21 +3091,11 @@
           <t>2020-07-28</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2020-07-28</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3494,11 +3104,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>RÖNN</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3515,15 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>88470669</v>
+        <v>88404243</v>
       </c>
       <c r="B27" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3531,37 +3131,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>3242</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bije-lite, V, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519955.8543639083</v>
+        <v>520565</v>
       </c>
       <c r="R27" t="n">
-        <v>7201347.913834508</v>
+        <v>7202360</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,22 +3185,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3615,27 +3205,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linnea Helmersson, Caspar Ström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>88470666</v>
+        <v>88459182</v>
       </c>
       <c r="B28" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3643,34 +3228,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>3242</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520041.1436647442</v>
+        <v>520548</v>
       </c>
       <c r="R28" t="n">
-        <v>7201294.19478097</v>
+        <v>7202309</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3697,22 +3282,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3732,44 +3307,39 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linnea Helmersson, Caspar Ström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>88459182</v>
+        <v>88459157</v>
       </c>
       <c r="B29" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3242</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3779,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520547.9984200731</v>
+        <v>520167</v>
       </c>
       <c r="R29" t="n">
-        <v>7202309.041756845</v>
+        <v>7202021</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3812,19 +3382,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3851,15 +3411,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>88459051</v>
+        <v>88459044</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,21 +3422,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3891,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520128.0768521114</v>
+        <v>520745</v>
       </c>
       <c r="R30" t="n">
-        <v>7201942.796031917</v>
+        <v>7201490</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3924,19 +3479,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3963,53 +3508,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>88470670</v>
+        <v>88404364</v>
       </c>
       <c r="B31" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>4660</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bije-lite, V, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520004.8964710536</v>
+        <v>520900</v>
       </c>
       <c r="R31" t="n">
-        <v>7201316.855554732</v>
+        <v>7201390</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4033,22 +3573,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4063,73 +3593,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linnea Helmersson, Caspar Ström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>88459170</v>
+        <v>87185933</v>
       </c>
       <c r="B32" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Vijnievaartoe NO, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520391.8465519027</v>
+        <v>520060</v>
       </c>
       <c r="R32" t="n">
-        <v>7202299.068278749</v>
+        <v>7201449</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4153,22 +3670,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4183,65 +3690,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Caspar Ström, Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>88459034</v>
+        <v>87185935</v>
       </c>
       <c r="B33" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Vijnievaartoe NO, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520917.0903503295</v>
+        <v>519991</v>
       </c>
       <c r="R33" t="n">
-        <v>7201310.798001057</v>
+        <v>7201317</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4265,22 +3767,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4295,65 +3787,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Caspar Ström, Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>88470660</v>
+        <v>88404534</v>
       </c>
       <c r="B34" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bije-lite, V, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520028.1629104555</v>
+        <v>520205</v>
       </c>
       <c r="R34" t="n">
-        <v>7201456.973448364</v>
+        <v>7202122</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4377,22 +3864,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4407,49 +3884,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linnea Helmersson, Caspar Ström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>88459157</v>
+        <v>88459051</v>
       </c>
       <c r="B35" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4459,10 +3931,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520167.0329173831</v>
+        <v>520128</v>
       </c>
       <c r="R35" t="n">
-        <v>7202021.082657721</v>
+        <v>7201943</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4492,19 +3964,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4531,37 +3993,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>88459037</v>
+        <v>88459169</v>
       </c>
       <c r="B36" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4571,10 +4028,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520912.1672457373</v>
+        <v>520392</v>
       </c>
       <c r="R36" t="n">
-        <v>7201346.815277359</v>
+        <v>7202299</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4604,19 +4061,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4643,50 +4090,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>88459033</v>
+        <v>88470659</v>
       </c>
       <c r="B37" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Vijnievaartoe NO, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520781.1577867833</v>
+        <v>519868</v>
       </c>
       <c r="R37" t="n">
-        <v>7201317.060495165</v>
+        <v>7201407</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4713,22 +4155,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4748,22 +4180,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Linnea Helmersson, Caspar Ström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>88459036</v>
+        <v>88404574</v>
       </c>
       <c r="B38" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,45 +4198,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Bije-lite, V, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520899.941988414</v>
+        <v>520565</v>
       </c>
       <c r="R38" t="n">
-        <v>7201334.005710203</v>
+        <v>7202360</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4836,19 +4255,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4863,7 +4272,7 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -4875,53 +4284,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>88470656</v>
+        <v>88404247</v>
       </c>
       <c r="B39" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bije-lite, V, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519868.0232410313</v>
+        <v>520155</v>
       </c>
       <c r="R39" t="n">
-        <v>7201401.193295168</v>
+        <v>7201939</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4945,22 +4349,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4975,49 +4369,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linnea Helmersson, Caspar Ström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>88470657</v>
+        <v>88470658</v>
       </c>
       <c r="B40" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5027,10 +4416,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519868.0119678068</v>
+        <v>519892</v>
       </c>
       <c r="R40" t="n">
-        <v>7201402.889721075</v>
+        <v>7201444</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5060,21 +4449,11 @@
           <t>2020-07-28</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2020-07-28</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5083,6 +4462,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>RÖNN</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5099,50 +4483,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>88459047</v>
+        <v>88470668</v>
       </c>
       <c r="B41" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Vijnievaartoe NO, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520153.1520248023</v>
+        <v>519956</v>
       </c>
       <c r="R41" t="n">
-        <v>7202001.907254887</v>
+        <v>7201348</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5169,22 +4548,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,22 +4573,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Linnea Helmersson, Caspar Ström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>88459040</v>
+        <v>88404567</v>
       </c>
       <c r="B42" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5227,45 +4591,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Bije-lite, V, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520716.9163510823</v>
+        <v>520565</v>
       </c>
       <c r="R42" t="n">
-        <v>7201518.073982552</v>
+        <v>7202360</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5292,19 +4648,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5319,7 +4665,7 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5331,15 +4677,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>88459049</v>
+        <v>88404310</v>
       </c>
       <c r="B43" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5347,37 +4688,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Bije-lite, V, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520130.2109879408</v>
+        <v>520151</v>
       </c>
       <c r="R43" t="n">
-        <v>7201941.114205981</v>
+        <v>7201876</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5404,19 +4750,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5431,7 +4767,7 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -5443,15 +4779,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>88459045</v>
+        <v>88404318</v>
       </c>
       <c r="B44" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5459,37 +4790,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Bije-lite, V, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520744.8098215121</v>
+        <v>520211</v>
       </c>
       <c r="R44" t="n">
-        <v>7201475.856038282</v>
+        <v>7202119</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5516,19 +4852,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5543,7 +4869,7 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -5555,15 +4881,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>88459057</v>
+        <v>88459036</v>
       </c>
       <c r="B45" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5571,34 +4892,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520163.981104453</v>
+        <v>520900</v>
       </c>
       <c r="R45" t="n">
-        <v>7202032.935115784</v>
+        <v>7201334</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5628,19 +4957,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5667,15 +4986,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>88470659</v>
+        <v>88459040</v>
       </c>
       <c r="B46" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5683,34 +4997,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519867.9837847677</v>
+        <v>520717</v>
       </c>
       <c r="R46" t="n">
-        <v>7201407.130781644</v>
+        <v>7201518</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5737,22 +5059,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5772,57 +5084,60 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linnea Helmersson, Caspar Ström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>88470668</v>
+        <v>88459046</v>
       </c>
       <c r="B47" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519955.8543639083</v>
+        <v>520151</v>
       </c>
       <c r="R47" t="n">
-        <v>7201347.913834508</v>
+        <v>7202001</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5849,22 +5164,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5884,22 +5189,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linnea Helmersson, Caspar Ström</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>88459046</v>
+        <v>88459170</v>
       </c>
       <c r="B48" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5939,10 +5239,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520151.035070523</v>
+        <v>520392</v>
       </c>
       <c r="R48" t="n">
-        <v>7202001.044900539</v>
+        <v>7202299</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5972,19 +5272,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6011,15 +5301,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>88459043</v>
+        <v>88470667</v>
       </c>
       <c r="B49" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6027,34 +5312,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Vijnievaartoe NO, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>520716.0465744403</v>
+        <v>520004</v>
       </c>
       <c r="R49" t="n">
-        <v>7201521.036728237</v>
+        <v>7201251</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6081,22 +5374,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6116,57 +5399,61 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Linnea Helmersson, Caspar Ström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>88459050</v>
+        <v>88459056</v>
       </c>
       <c r="B50" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>48</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520130.2109879408</v>
+        <v>520262</v>
       </c>
       <c r="R50" t="n">
-        <v>7201941.114205981</v>
+        <v>7201687</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6196,27 +5483,18 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6235,50 +5513,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>88459042</v>
+        <v>87185868</v>
       </c>
       <c r="B51" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1467</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bijelite, Ås lm</t>
+          <t>Vijnievaartoe NO, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520725.1660844101</v>
+        <v>519968</v>
       </c>
       <c r="R51" t="n">
-        <v>7201491.83618771</v>
+        <v>7201462</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6305,22 +5578,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6335,69 +5598,65 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Linnea Helmersson, Caspar Ström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>87185805</v>
+        <v>88404427</v>
       </c>
       <c r="B52" t="n">
-        <v>57073</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103056</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bije-lite, V, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519995.8158394768</v>
+        <v>520190</v>
       </c>
       <c r="R52" t="n">
-        <v>7201468.208087415</v>
+        <v>7202083</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6421,22 +5680,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6451,27 +5700,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Caspar Ström, Linnea Helmersson</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>87185868</v>
+        <v>88459041</v>
       </c>
       <c r="B53" t="n">
-        <v>57657</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6499,14 +5743,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vijnievaartoe NO, Ås lm</t>
+          <t>Bijelite, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519968</v>
+        <v>520565</v>
       </c>
       <c r="R53" t="n">
-        <v>7201462</v>
+        <v>7201537</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6533,12 +5777,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6553,15 +5797,601 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
+          <t>Linnea Helmersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>87185805</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58656</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Vijnievaartoe NO, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>519996</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7201468</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
           <t>Caspar Ström</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson, Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>87185949</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Vijnievaartoe NO, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>519891</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7201388</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
         <is>
           <t>Caspar Ström, Linnea Helmersson</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>88470656</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vijnievaartoe NO, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>519868</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7201401</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson, Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>87185848</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vijnievaartoe NO, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>519906</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7201433</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson, Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>87185837</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Vijnievaartoe NO, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>519915</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7201337</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson, Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>88470657</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Vijnievaartoe NO, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>519868</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7201403</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson, Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
